--- a/output/training_result_databaru/frequent_itemsets_70_30.xlsx
+++ b/output/training_result_databaru/frequent_itemsets_70_30.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Anisa', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'operator_Anisa'})</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb night brightening', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_hb night brightening'})</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'operator_Riska', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'operator_Riska', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket brightening', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_paket brightening'})</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket brightening', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket brightening'})</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket brightening', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_paket brightening'})</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_paket brightening'})</t>
+          <t>frozenset({'produk_paket brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_sunscreen oily acne new'})</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket custom', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket custom'})</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'waktu_Siang', 'produk_night cream brightening'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_night cream brightening', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'operator_Indah', 'produk_night cream brightening'})</t>
+          <t>frozenset({'operator_Indah', 'produk_night cream brightening', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Indah', 'produk_night cream brightening'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Siang', 'produk_night cream brightening'})</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Indah', 'produk_night cream brightening'})</t>
+          <t>frozenset({'operator_Indah', 'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Oktavira', 'produk_night cream brightening'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_sunscreen glowing new'})</t>
+          <t>frozenset({'produk_sunscreen glowing new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_daily ceramois hydra gel'})</t>
+          <t>frozenset({'produk_daily ceramois hydra gel', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket radian brightening ultimate', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_facial wash oily acne 110 ml new'})</t>
+          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Riska', 'waktu_Siang'})</t>
+          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'waktu_Siang', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket acne brightening', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket acne brightening'})</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>frozenset({'produk_bb chusion flawless', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_bb chusion flawless'})</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb night yellow plus licorice', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_hb night yellow plus licorice'})</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb night yellow plus licorice', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_hb night yellow plus licorice'})</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
